--- a/tame_output/ON/bt/strategyON_20231120.xlsx
+++ b/tame_output/ON/bt/strategyON_20231120.xlsx
@@ -595,12 +595,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>88.7%</t>
+          <t>90.5%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,12 +839,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>24.6%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -916,11 +916,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.1%</t>
+          <t>453.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-20.3%</t>
+          <t>-20.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.9%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>103.5%</t>
+          <t>103.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-18.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>30.5%</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-156.9%</t>
+          <t>-156.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>133.5%</t>
+          <t>133.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,16 +1370,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>127.4%</t>
+          <t>127.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>30.3%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1786"/>
+  <dimension ref="A1:G1787"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42588,7 +42588,7 @@
         <v>45248</v>
       </c>
       <c r="B1786" t="n">
-        <v>3.122211734044351</v>
+        <v>3.12341686637382</v>
       </c>
       <c r="C1786" t="n">
         <v>3.090962466394117</v>
@@ -42604,6 +42604,29 @@
       </c>
       <c r="G1786" t="n">
         <v>4.403233633632199</v>
+      </c>
+    </row>
+    <row r="1787">
+      <c r="A1787" s="2" t="n">
+        <v>45249</v>
+      </c>
+      <c r="B1787" t="n">
+        <v>3.140086936175495</v>
+      </c>
+      <c r="C1787" t="n">
+        <v>3.100925124196311</v>
+      </c>
+      <c r="D1787" t="n">
+        <v>1.572743859318631</v>
+      </c>
+      <c r="E1787" t="n">
+        <v>3.729666243610017</v>
+      </c>
+      <c r="F1787" t="n">
+        <v>2.187118612063468</v>
+      </c>
+      <c r="G1787" t="n">
+        <v>4.413196291434393</v>
       </c>
     </row>
   </sheetData>
